--- a/public/apresentacao/CRM-Prospeccao-Excel.xlsx
+++ b/public/apresentacao/CRM-Prospeccao-Excel.xlsx
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CRM!$A$4:$AL$204</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Pendentes!$A$4:$AL$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Pendentes!$A$4:$AL$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Qualificados!$A$4:$AL$6</definedName>
     <definedName name="Etapas">'Listas'!$A$1:$A$9</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="481">
   <si>
     <t>Prospectar</t>
   </si>
@@ -616,6 +616,375 @@
     <t>Localizar contato comercial atual fora do Instagram</t>
   </si>
   <si>
+    <t>Onodera Estética</t>
+  </si>
+  <si>
+    <t>Rede nacional</t>
+  </si>
+  <si>
+    <t>+55 11 99912-1430</t>
+  </si>
+  <si>
+    <t>https://www.onodera.com.br/</t>
+  </si>
+  <si>
+    <t>Já oferece agendamento online, cadastro e comércio eletrônico; maior oportunidade seria integração ou piloto autorizado por unidade.</t>
+  </si>
+  <si>
+    <t>Confirmar proprietário brasileiro e decisor; perguntar sobre integração e autonomia da unidade.</t>
+  </si>
+  <si>
+    <t>Central publicada é de apoio ao e-commerce; pedir encaminhamento à gestão. Não equivale ao contato direto do dono.</t>
+  </si>
+  <si>
+    <t>Rede anuncia mais de 50 clínicas e operação desde 1981; estrutura digital madura, sem verba de compra confirmada.</t>
+  </si>
+  <si>
+    <t>Emagrecentro</t>
+  </si>
+  <si>
+    <t>+55 11 94585-8889</t>
+  </si>
+  <si>
+    <t>https://www.emagrecentro.com.br/</t>
+  </si>
+  <si>
+    <t>Já divulga aplicativo de acompanhamento e formulário de avaliação. Investigar integrações, sem oferecer área do cliente como novidade garantida.</t>
+  </si>
+  <si>
+    <t>Site esclarece que é clínica de emagrecimento com aparelhos e não clínica médica.</t>
+  </si>
+  <si>
+    <t>Rede, aplicativo, portal de franqueado e variedade de tratamentos divulgados; contadores dinâmicos em zero não foram usados como dados.</t>
+  </si>
+  <si>
+    <t>Espaçolaser</t>
+  </si>
+  <si>
+    <t>+55 11 97490-4291</t>
+  </si>
+  <si>
+    <t>https://www.espacolaser.com.br/</t>
+  </si>
+  <si>
+    <t>Já tem acesso à conta, agendamento e comércio eletrônico; pouca aderência à venda de um site simples.</t>
+  </si>
+  <si>
+    <t>WhatsApp publicado para dúvidas do e-commerce. Identificar autonomia do franqueado/gestão; não presumir dono único brasileiro.</t>
+  </si>
+  <si>
+    <t>Rede com busca de unidades, ofertas de pacotes e plataforma de clientes; contratação corporativa a investigar.</t>
+  </si>
+  <si>
+    <t>Buddha Spa</t>
+  </si>
+  <si>
+    <t>https://www.buddhaspa.com.br/</t>
+  </si>
+  <si>
+    <t>Já possui conta, pedidos e vouchers. Oferecer integração/piloto apenas após descobrir lacunas de atendimento.</t>
+  </si>
+  <si>
+    <t>Formulário permite selecionar Comercial e Parcerias. WhatsApp SAC publicado: +55 11 99620-2678; não usado como contato direto de vendas.</t>
+  </si>
+  <si>
+    <t>Formulário: departamento Comercial e Parcerias</t>
+  </si>
+  <si>
+    <t>https://buddhaspa.com.br/o-buddha-spa/contato/</t>
+  </si>
+  <si>
+    <t>Rede em vários estados, estética facial/corporal e comércio de serviços/produtos; sinais de operação estruturada.</t>
+  </si>
+  <si>
+    <t>OligoFlora</t>
+  </si>
+  <si>
+    <t>+55 11 99794-5157</t>
+  </si>
+  <si>
+    <t>https://www.oligoflora.com.br/</t>
+  </si>
+  <si>
+    <t>Formulário coleta unidade e preferência de horário para retorno; validar se a gestão já possui área do cliente e painel integrados.</t>
+  </si>
+  <si>
+    <t>Confirmar proprietário brasileiro e decisor; validar sistema atual e oferecer demonstração do fluxo de solicitação/aprovação.</t>
+  </si>
+  <si>
+    <t>Formulário visível é solicitação de contato, não confirmação instantânea de horário.</t>
+  </si>
+  <si>
+    <t>Sede licenciadora, múltiplas unidades e categorias facial/corporal/bem-estar divulgadas; não há orçamento publicado.</t>
+  </si>
+  <si>
+    <t>Grupo Adriana Vilarinho</t>
+  </si>
+  <si>
+    <t>Adriana Vilarinho (fundadora)</t>
+  </si>
+  <si>
+    <t>+55 11 3032-1000</t>
+  </si>
+  <si>
+    <t>https://www.adrianavilarinho.com.br/</t>
+  </si>
+  <si>
+    <t>Chamadas de agendamento levam ao WhatsApp; oportunidade potencial em acompanhamento e organização por unidade, respeitando sistema existente.</t>
+  </si>
+  <si>
+    <t>Ser reconhecida no mercado brasileiro e formada no Brasil não comprova nacionalidade.</t>
+  </si>
+  <si>
+    <t>Página institucional anuncia cinco unidades e mais de 130 profissionais; serviços clínicos, faciais, corporais e capilares.</t>
+  </si>
+  <si>
+    <t>https://www.adrianavilarinho.com.br/sobre-nos</t>
+  </si>
+  <si>
+    <t>Clínica Vanessa Metz</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro/RJ</t>
+  </si>
+  <si>
+    <t>Vanessa Metz (proprietária fundadora)</t>
+  </si>
+  <si>
+    <t>https://www.clinicavanessametz.com.br/</t>
+  </si>
+  <si>
+    <t>Site apresenta tratamentos e convite para agendar; demonstrar solicitações de consulta e atualização do catálogo pela equipe.</t>
+  </si>
+  <si>
+    <t>Número móvel publicado em Contato; link WhatsApp não capturado com destino verificável, por isso canal marcado como Telefone.</t>
+  </si>
+  <si>
+    <t>+55 21 98292-1357</t>
+  </si>
+  <si>
+    <t>Proprietária identificada, equipe e linhas de rejuvenescimento, corporal, capilar e procedimentos cirúrgicos.</t>
+  </si>
+  <si>
+    <t>Clínica Luciana Pepino</t>
+  </si>
+  <si>
+    <t>Localização a confirmar</t>
+  </si>
+  <si>
+    <t>Luciana Pepino (profissional identificada; propriedade a confirmar)</t>
+  </si>
+  <si>
+    <t>https://www.lucianapepino.com.br/</t>
+  </si>
+  <si>
+    <t>Clínica com forte foco cirúrgico; avaliar demanda de estética e jornada da consulta antes de propor um produto pensado para estética.</t>
+  </si>
+  <si>
+    <t>Telefone com DDD 11 publicado. Cidade/endereço e propriedade não foram inferidos. Página institucional retornou conteúdo parcialmente carregado.</t>
+  </si>
+  <si>
+    <t>+55 11 3285-6412</t>
+  </si>
+  <si>
+    <t>Profissionais experientes e diversas especialidades cirúrgicas publicadas; não extrapolar orçamento a partir do nome médico.</t>
+  </si>
+  <si>
+    <t>Clínica Daniela Lemes</t>
+  </si>
+  <si>
+    <t>Daniela Lemes (profissional identificada; propriedade a confirmar)</t>
+  </si>
+  <si>
+    <t>+55 21 99999-5633</t>
+  </si>
+  <si>
+    <t>https://www.danielalemes.com.br/</t>
+  </si>
+  <si>
+    <t>Site com tecnologias e atendimento pelo WhatsApp; possível oportunidade de manutenção de conteúdo e solicitações organizadas.</t>
+  </si>
+  <si>
+    <t>Página contém texto/links de cassino sem relação com a clínica. Revalidar contato e situação do site; não afirmar causa ou invasão sem análise adicional.</t>
+  </si>
+  <si>
+    <t>Clínica física, tecnologias estéticas nomeadas e profissional especializada apresentada no site.</t>
+  </si>
+  <si>
+    <t>Clínica Helena Costa</t>
+  </si>
+  <si>
+    <t>Helena Costa (médica responsável; propriedade a confirmar)</t>
+  </si>
+  <si>
+    <t>+55 21 97136-9883</t>
+  </si>
+  <si>
+    <t>https://www.clinicahelenacosta.com.br/</t>
+  </si>
+  <si>
+    <t>Atendimento pelo WhatsApp; serviços dermatológicos, capilares e estéticos permitem apresentar gestão de conteúdo e acompanhamento.</t>
+  </si>
+  <si>
+    <t>contato@clinicahelenacosta.com.br. Página institucional contém link alheio a cassino; confirmar situação atual antes da proposta.</t>
+  </si>
+  <si>
+    <t>Clínica física no Leblon, múltiplas linhas de tratamento e responsável técnica identificada.</t>
+  </si>
+  <si>
+    <t>https://clinicahelenacosta.com.br/clinica/</t>
+  </si>
+  <si>
+    <t>Royal Face</t>
+  </si>
+  <si>
+    <t>contato@royalface.com.br</t>
+  </si>
+  <si>
+    <t>https://www.royalface.com.br/</t>
+  </si>
+  <si>
+    <t>Já possui compra online, portal e agendamento; oportunidade de integração depende de processo de compra corporativo.</t>
+  </si>
+  <si>
+    <t>Telefone público +55 41 98707-2823. Fundadores/sócios atuais e origem brasileira não confirmados nesta rodada.</t>
+  </si>
+  <si>
+    <t>E-mail</t>
+  </si>
+  <si>
+    <t>Página Sobre divulga mais de 300 unidades comercializadas, operação em 25 estados e DF; unidades comercializadas não equivalem a unidades abertas.</t>
+  </si>
+  <si>
+    <t>Clínica Bergmann</t>
+  </si>
+  <si>
+    <t>Porto Alegre/RS</t>
+  </si>
+  <si>
+    <t>Julio Bergmann (médico identificado; propriedade a confirmar)</t>
+  </si>
+  <si>
+    <t>+55 51 99570-6643</t>
+  </si>
+  <si>
+    <t>https://www.clinicabergmann.com.br/</t>
+  </si>
+  <si>
+    <t>Catálogo extenso e consulta online divulgada; confirmar funcionamento existente e propor jornada de solicitação e acompanhamento capilar/facial.</t>
+  </si>
+  <si>
+    <t>Rodapé identifica explicitamente o número como WhatsApp; contato@clinicabergmann.com.br. Não afirmar ausência de consulta online.</t>
+  </si>
+  <si>
+    <t>Endereço físico, equipamentos, tratamentos faciais/corporais/capilares e médico identificado.</t>
+  </si>
+  <si>
+    <t>Clínica Slim Tratamento Capilar</t>
+  </si>
+  <si>
+    <t>São Paulo/SP; Jundiaí/SP</t>
+  </si>
+  <si>
+    <t>https://www.clinicaslim.com.br/</t>
+  </si>
+  <si>
+    <t>Tratamentos capilares recorrentes combinam com acompanhamento privado e solicitações; confirmar processo atual de agenda.</t>
+  </si>
+  <si>
+    <t>Número móvel da unidade São Paulo; não presumir WhatsApp. Site mostra divergência entre 44 e 46 anos e muitos links alheios de apostas. Revalidar contato antes de abordagem.</t>
+  </si>
+  <si>
+    <t>+55 11 97276-9705</t>
+  </si>
+  <si>
+    <t>Duas unidades/endereço e tecnologias capilares publicados; equipe e verba atual não comprovadas.</t>
+  </si>
+  <si>
+    <t>Elegance Estética</t>
+  </si>
+  <si>
+    <t>Bauru/SP</t>
+  </si>
+  <si>
+    <t>Felipe Alves (responsável técnico; propriedade a confirmar)</t>
+  </si>
+  <si>
+    <t>+55 14 99845-5678</t>
+  </si>
+  <si>
+    <t>https://www.eleganceestetica.com.br/</t>
+  </si>
+  <si>
+    <t>Página apresenta tratamentos e leva contato ao WhatsApp; alta aderência aparente à edição de catálogo e solicitação de avaliação.</t>
+  </si>
+  <si>
+    <t>CNPJ 59.187.109/0001-22. Rodapé e CTAs principais repetem o número escolhido; outro link diverge e não foi usado.</t>
+  </si>
+  <si>
+    <t>Unidade/endereço, biomédico responsável, criofrequência e procedimentos faciais/corporais divulgados; parcelamento não prova verba disponível.</t>
+  </si>
+  <si>
+    <t>Botoclinic</t>
+  </si>
+  <si>
+    <t>sac@botoclinic.com</t>
+  </si>
+  <si>
+    <t>https://www.botoclinic.com/</t>
+  </si>
+  <si>
+    <t>Site divulga agendamento, aplicativo e unidades; venda de site simples tem baixa aderência. Investigar piloto/integracão com aprovação corporativa.</t>
+  </si>
+  <si>
+    <t>SAC é canal para pedir encaminhamento ao setor comercial, não decisor direto. CNPJ 31.324.392/0001-78; .com.br redireciona à mesma marca, contado uma única vez.</t>
+  </si>
+  <si>
+    <t>Rede, aplicativo, clube e catálogo de harmonização/tecnologias publicados; estrutura corporativa, sem orçamento confirmado.</t>
+  </si>
+  <si>
+    <t>Clínica Seven</t>
+  </si>
+  <si>
+    <t>+55 11 4933-1719</t>
+  </si>
+  <si>
+    <t>https://www.clinicaseven.com.br/</t>
+  </si>
+  <si>
+    <t>Chamadas de consulta levam ao WhatsApp; acompanhamento médico/nutricional pode se beneficiar de jornada integrada, a validar.</t>
+  </si>
+  <si>
+    <t>Segmento de longevidade/emagrecimento, aderência diferente de estética facial. SAC: sac@clinicaseven.com.br; proprietário não identificado.</t>
+  </si>
+  <si>
+    <t>Clínica física, equipe médica/nutricional e mais de 15 anos anunciados; foco em emagrecimento e definição corporal.</t>
+  </si>
+  <si>
+    <t>Clínica HA Gestão em Medicina Avançada</t>
+  </si>
+  <si>
+    <t>Curitiba/PR</t>
+  </si>
+  <si>
+    <t>Harielle Asega (diretora técnica; propriedade a confirmar)</t>
+  </si>
+  <si>
+    <t>+55 41 98501-4101</t>
+  </si>
+  <si>
+    <t>https://www.clinicaha.com.br/</t>
+  </si>
+  <si>
+    <t>Agendamento pelo WhatsApp e catálogo dermatológico/estético/capilar; avaliar organização de solicitações e acompanhamento por serviço.</t>
+  </si>
+  <si>
+    <t>atendimento@hadermatologia.com.br. Ser diretora técnica não comprova propriedade ou nacionalidade.</t>
+  </si>
+  <si>
+    <t>Clínica física, múltiplas especialidades e direção técnica identificada; não inferir verba por volume autodeclarado de transplantes.</t>
+  </si>
+  <si>
     <t>CRM de clínicas • Qualificados</t>
   </si>
   <si>
@@ -715,7 +1084,7 @@
     <t>Escopo</t>
   </si>
   <si>
-    <t>Levantamento inicial de 13 candidatos, não estudo censitário nem garantia de vendas. Consulta pública em 07/10/2026; fontes antigas identificadas explicitamente.</t>
+    <t>Levantamento inicial de 30 candidatos, não estudo censitário nem garantia de vendas. Consulta pública em 07/10/2026; fontes antigas identificadas explicitamente.</t>
   </si>
   <si>
     <t>Dimensão</t>
@@ -960,6 +1329,125 @@
   </si>
   <si>
     <t>FORA DO BRASIL. Reportagem de 29/04/2022; site bloqueou acesso automatizado. brazilicious.com é comércio de pão de queijo e não pertence a este registro. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.onodera.com.br/
+</t>
+  </si>
+  <si>
+    <t>Central publicada é de apoio ao e-commerce; pedir encaminhamento à gestão. Não equivale ao contato direto do dono. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.emagrecentro.com.br/
+</t>
+  </si>
+  <si>
+    <t>Site esclarece que é clínica de emagrecimento com aparelhos e não clínica médica. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.espacolaser.com.br/
+</t>
+  </si>
+  <si>
+    <t>WhatsApp publicado para dúvidas do e-commerce. Identificar autonomia do franqueado/gestão; não presumir dono único brasileiro. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://buddhaspa.com.br/o-buddha-spa/contato/
+</t>
+  </si>
+  <si>
+    <t>Formulário permite selecionar Comercial e Parcerias. WhatsApp SAC publicado: +55 11 99620-2678; não usado como contato direto de vendas. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.oligoflora.com.br/
+</t>
+  </si>
+  <si>
+    <t>Formulário visível é solicitação de contato, não confirmação instantânea de horário. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t>https://www.adrianavilarinho.com.br/
+https://www.adrianavilarinho.com.br/sobre-nos</t>
+  </si>
+  <si>
+    <t>Ser reconhecida no mercado brasileiro e formada no Brasil não comprova nacionalidade. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t>https://www.clinicavanessametz.com.br/
+https://www.clinicavanessametz.com.br/</t>
+  </si>
+  <si>
+    <t>Número móvel publicado em Contato; link WhatsApp não capturado com destino verificável, por isso canal marcado como Telefone. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t>https://www.lucianapepino.com.br/
+https://www.lucianapepino.com.br/</t>
+  </si>
+  <si>
+    <t>Telefone com DDD 11 publicado. Cidade/endereço e propriedade não foram inferidos. Página institucional retornou conteúdo parcialmente carregado. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t>https://www.danielalemes.com.br/
+https://www.danielalemes.com.br/</t>
+  </si>
+  <si>
+    <t>Página contém texto/links de cassino sem relação com a clínica. Revalidar contato e situação do site; não afirmar causa ou invasão sem análise adicional. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t>https://www.clinicahelenacosta.com.br/
+https://clinicahelenacosta.com.br/clinica/</t>
+  </si>
+  <si>
+    <t>contato@clinicahelenacosta.com.br. Página institucional contém link alheio a cassino; confirmar situação atual antes da proposta. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.royalface.com.br/
+</t>
+  </si>
+  <si>
+    <t>Telefone público +55 41 98707-2823. Fundadores/sócios atuais e origem brasileira não confirmados nesta rodada. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t>https://www.clinicabergmann.com.br/
+https://www.clinicabergmann.com.br/</t>
+  </si>
+  <si>
+    <t>Rodapé identifica explicitamente o número como WhatsApp; contato@clinicabergmann.com.br. Não afirmar ausência de consulta online. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.clinicaslim.com.br/
+</t>
+  </si>
+  <si>
+    <t>Número móvel da unidade São Paulo; não presumir WhatsApp. Site mostra divergência entre 44 e 46 anos e muitos links alheios de apostas. Revalidar contato antes de abordagem. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t>https://www.eleganceestetica.com.br/
+https://www.eleganceestetica.com.br/</t>
+  </si>
+  <si>
+    <t>CNPJ 59.187.109/0001-22. Rodapé e CTAs principais repetem o número escolhido; outro link diverge e não foi usado. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.botoclinic.com/
+</t>
+  </si>
+  <si>
+    <t>SAC é canal para pedir encaminhamento ao setor comercial, não decisor direto. CNPJ 31.324.392/0001-78; .com.br redireciona à mesma marca, contado uma única vez. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.clinicaseven.com.br/
+</t>
+  </si>
+  <si>
+    <t>Segmento de longevidade/emagrecimento, aderência diferente de estética facial. SAC: sac@clinicaseven.com.br; proprietário não identificado. Consulta em 07/10/2026.</t>
+  </si>
+  <si>
+    <t>https://www.clinicaha.com.br/
+https://www.clinicaha.com.br/</t>
+  </si>
+  <si>
+    <t>atendimento@hadermatologia.com.br. Ser diretora técnica não comprova propriedade ou nacionalidade. Consulta em 07/10/2026.</t>
   </si>
   <si>
     <t>ISAPS</t>
@@ -1463,46 +1951,46 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>312</v>
+        <v>469</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>313</v>
+        <v>470</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>314</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="100" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>315</v>
+        <v>472</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>316</v>
+        <v>473</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>317</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="100" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>318</v>
+        <v>475</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>319</v>
+        <v>476</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>320</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="100" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>321</v>
+        <v>478</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>322</v>
+        <v>479</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>323</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -3056,177 +3544,1749 @@
         <v>194</v>
       </c>
     </row>
-    <row r="18" spans="1:38">
-      <c r="S18" s="5">
+    <row r="18" spans="1:38" ht="88" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="S18" s="5" t="str">
         <f>IF(A18="","",IF(H18="Fechado","Fechado",IF(H18="Perdido","Perdido",IF(K18="","Sem data",IF(K18&lt;TODAY(),"Atrasado",IF(K18=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD18" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="X18" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="AD18" s="5" t="str">
         <f>IF(A18="","",IF(OR(AK18&lt;&gt;"Qualificado",Y18&lt;&gt;"Verificado",U18="",Z18="",AA18=""),"Pendente",IF(AND(Z18&gt;=7,AA18&gt;=6),"Alta",IF(AND(Z18&gt;=5,AA18&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:38">
-      <c r="S19" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL18" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" ht="88" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="S19" s="5" t="str">
         <f>IF(A19="","",IF(H19="Fechado","Fechado",IF(H19="Perdido","Perdido",IF(K19="","Sem data",IF(K19&lt;TODAY(),"Atrasado",IF(K19=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD19" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="X19" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="AC19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD19" s="5" t="str">
         <f>IF(A19="","",IF(OR(AK19&lt;&gt;"Qualificado",Y19&lt;&gt;"Verificado",U19="",Z19="",AA19=""),"Pendente",IF(AND(Z19&gt;=7,AA19&gt;=6),"Alta",IF(AND(Z19&gt;=5,AA19&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:38">
-      <c r="S20" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL19" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" ht="88" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="S20" s="5" t="str">
         <f>IF(A20="","",IF(H20="Fechado","Fechado",IF(H20="Perdido","Perdido",IF(K20="","Sem data",IF(K20&lt;TODAY(),"Atrasado",IF(K20=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD20" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="X20" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>2</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD20" s="5" t="str">
         <f>IF(A20="","",IF(OR(AK20&lt;&gt;"Qualificado",Y20&lt;&gt;"Verificado",U20="",Z20="",AA20=""),"Pendente",IF(AND(Z20&gt;=7,AA20&gt;=6),"Alta",IF(AND(Z20&gt;=5,AA20&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:38">
-      <c r="S21" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL20" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" ht="88" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="S21" s="5" t="str">
         <f>IF(A21="","",IF(H21="Fechado","Fechado",IF(H21="Perdido","Perdido",IF(K21="","Sem data",IF(K21&lt;TODAY(),"Atrasado",IF(K21=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD21" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="W21" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="X21" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD21" s="5" t="str">
         <f>IF(A21="","",IF(OR(AK21&lt;&gt;"Qualificado",Y21&lt;&gt;"Verificado",U21="",Z21="",AA21=""),"Pendente",IF(AND(Z21&gt;=7,AA21&gt;=6),"Alta",IF(AND(Z21&gt;=5,AA21&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:38">
-      <c r="S22" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL21" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" ht="88" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="S22" s="5" t="str">
         <f>IF(A22="","",IF(H22="Fechado","Fechado",IF(H22="Perdido","Perdido",IF(K22="","Sem data",IF(K22&lt;TODAY(),"Atrasado",IF(K22=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD22" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="X22" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AD22" s="5" t="str">
         <f>IF(A22="","",IF(OR(AK22&lt;&gt;"Qualificado",Y22&lt;&gt;"Verificado",U22="",Z22="",AA22=""),"Pendente",IF(AND(Z22&gt;=7,AA22&gt;=6),"Alta",IF(AND(Z22&gt;=5,AA22&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:38">
-      <c r="S23" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL22" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" ht="88" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="S23" s="5" t="str">
         <f>IF(A23="","",IF(H23="Fechado","Fechado",IF(H23="Perdido","Perdido",IF(K23="","Sem data",IF(K23&lt;TODAY(),"Atrasado",IF(K23=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD23" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V23" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="W23" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="X23" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>6</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD23" s="5" t="str">
         <f>IF(A23="","",IF(OR(AK23&lt;&gt;"Qualificado",Y23&lt;&gt;"Verificado",U23="",Z23="",AA23=""),"Pendente",IF(AND(Z23&gt;=7,AA23&gt;=6),"Alta",IF(AND(Z23&gt;=5,AA23&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:38">
-      <c r="S24" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF23" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH23" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="AI23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL23" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" ht="88" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="S24" s="5" t="str">
         <f>IF(A24="","",IF(H24="Fechado","Fechado",IF(H24="Perdido","Perdido",IF(K24="","Sem data",IF(K24&lt;TODAY(),"Atrasado",IF(K24=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD24" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="X24" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD24" s="5" t="str">
         <f>IF(A24="","",IF(OR(AK24&lt;&gt;"Qualificado",Y24&lt;&gt;"Verificado",U24="",Z24="",AA24=""),"Pendente",IF(AND(Z24&gt;=7,AA24&gt;=6),"Alta",IF(AND(Z24&gt;=5,AA24&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:38">
-      <c r="S25" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH24" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL24" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" ht="88" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="S25" s="5" t="str">
         <f>IF(A25="","",IF(H25="Fechado","Fechado",IF(H25="Perdido","Perdido",IF(K25="","Sem data",IF(K25&lt;TODAY(),"Atrasado",IF(K25=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD25" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="W25" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="X25" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>5</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB25" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="AC25" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="AD25" s="5" t="str">
         <f>IF(A25="","",IF(OR(AK25&lt;&gt;"Qualificado",Y25&lt;&gt;"Verificado",U25="",Z25="",AA25=""),"Pendente",IF(AND(Z25&gt;=7,AA25&gt;=6),"Alta",IF(AND(Z25&gt;=5,AA25&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:38">
-      <c r="S26" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF25" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="AG25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH25" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="AI25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL25" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" ht="88" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="S26" s="5" t="str">
         <f>IF(A26="","",IF(H26="Fechado","Fechado",IF(H26="Perdido","Perdido",IF(K26="","Sem data",IF(K26&lt;TODAY(),"Atrasado",IF(K26=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD26" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="V26" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="W26" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="X26" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="AD26" s="5" t="str">
         <f>IF(A26="","",IF(OR(AK26&lt;&gt;"Qualificado",Y26&lt;&gt;"Verificado",U26="",Z26="",AA26=""),"Pendente",IF(AND(Z26&gt;=7,AA26&gt;=6),"Alta",IF(AND(Z26&gt;=5,AA26&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:38">
-      <c r="S27" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH26" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="AI26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL26" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" ht="88" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="S27" s="5" t="str">
         <f>IF(A27="","",IF(H27="Fechado","Fechado",IF(H27="Perdido","Perdido",IF(K27="","Sem data",IF(K27&lt;TODAY(),"Atrasado",IF(K27=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD27" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="V27" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="W27" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="X27" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="AD27" s="5" t="str">
         <f>IF(A27="","",IF(OR(AK27&lt;&gt;"Qualificado",Y27&lt;&gt;"Verificado",U27="",Z27="",AA27=""),"Pendente",IF(AND(Z27&gt;=7,AA27&gt;=6),"Alta",IF(AND(Z27&gt;=5,AA27&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:38">
-      <c r="S28" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH27" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="AI27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ27" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL27" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" ht="88" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="S28" s="5" t="str">
         <f>IF(A28="","",IF(H28="Fechado","Fechado",IF(H28="Perdido","Perdido",IF(K28="","Sem data",IF(K28&lt;TODAY(),"Atrasado",IF(K28=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD28" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="V28" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="W28" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="X28" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB28" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC28" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD28" s="5" t="str">
         <f>IF(A28="","",IF(OR(AK28&lt;&gt;"Qualificado",Y28&lt;&gt;"Verificado",U28="",Z28="",AA28=""),"Pendente",IF(AND(Z28&gt;=7,AA28&gt;=6),"Alta",IF(AND(Z28&gt;=5,AA28&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:38">
-      <c r="S29" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL28" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" ht="88" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="S29" s="5" t="str">
         <f>IF(A29="","",IF(H29="Fechado","Fechado",IF(H29="Perdido","Perdido",IF(K29="","Sem data",IF(K29&lt;TODAY(),"Atrasado",IF(K29=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD29" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="W29" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="X29" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="AD29" s="5" t="str">
         <f>IF(A29="","",IF(OR(AK29&lt;&gt;"Qualificado",Y29&lt;&gt;"Verificado",U29="",Z29="",AA29=""),"Pendente",IF(AND(Z29&gt;=7,AA29&gt;=6),"Alta",IF(AND(Z29&gt;=5,AA29&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:38">
-      <c r="S30" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH29" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" ht="88" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="S30" s="5" t="str">
         <f>IF(A30="","",IF(H30="Fechado","Fechado",IF(H30="Perdido","Perdido",IF(K30="","Sem data",IF(K30&lt;TODAY(),"Atrasado",IF(K30=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD30" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="U30" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="V30" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="W30" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="X30" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>6</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="AC30" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="AD30" s="5" t="str">
         <f>IF(A30="","",IF(OR(AK30&lt;&gt;"Qualificado",Y30&lt;&gt;"Verificado",U30="",Z30="",AA30=""),"Pendente",IF(AND(Z30&gt;=7,AA30&gt;=6),"Alta",IF(AND(Z30&gt;=5,AA30&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:38">
-      <c r="S31" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE30" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG30" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ30" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK30" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL30" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" ht="88" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="S31" s="5" t="str">
         <f>IF(A31="","",IF(H31="Fechado","Fechado",IF(H31="Perdido","Perdido",IF(K31="","Sem data",IF(K31&lt;TODAY(),"Atrasado",IF(K31=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD31" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U31" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="V31" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="W31" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="X31" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>8</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>6</v>
+      </c>
+      <c r="AB31" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="AC31" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="AD31" s="5" t="str">
         <f>IF(A31="","",IF(OR(AK31&lt;&gt;"Qualificado",Y31&lt;&gt;"Verificado",U31="",Z31="",AA31=""),"Pendente",IF(AND(Z31&gt;=7,AA31&gt;=6),"Alta",IF(AND(Z31&gt;=5,AA31&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:38">
-      <c r="S32" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF31" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="AG31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH31" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="AI31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ31" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL31" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" ht="88" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="S32" s="5" t="str">
         <f>IF(A32="","",IF(H32="Fechado","Fechado",IF(H32="Perdido","Perdido",IF(K32="","Sem data",IF(K32&lt;TODAY(),"Atrasado",IF(K32=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD32" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="V32" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="W32" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="X32" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="AD32" s="5" t="str">
         <f>IF(A32="","",IF(OR(AK32&lt;&gt;"Qualificado",Y32&lt;&gt;"Verificado",U32="",Z32="",AA32=""),"Pendente",IF(AND(Z32&gt;=7,AA32&gt;=6),"Alta",IF(AND(Z32&gt;=5,AA32&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="19:30">
-      <c r="S33" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH32" s="3"/>
+      <c r="AI32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK32" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL32" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" ht="88" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="S33" s="5" t="str">
         <f>IF(A33="","",IF(H33="Fechado","Fechado",IF(H33="Perdido","Perdido",IF(K33="","Sem data",IF(K33&lt;TODAY(),"Atrasado",IF(K33=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD33" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="V33" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="W33" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="X33" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>6</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB33" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD33" s="5" t="str">
         <f>IF(A33="","",IF(OR(AK33&lt;&gt;"Qualificado",Y33&lt;&gt;"Verificado",U33="",Z33="",AA33=""),"Pendente",IF(AND(Z33&gt;=7,AA33&gt;=6),"Alta",IF(AND(Z33&gt;=5,AA33&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="19:30">
-      <c r="S34" s="5">
+        <v>Pendente</v>
+      </c>
+      <c r="AE33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH33" s="3"/>
+      <c r="AI33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ33" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL33" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" ht="88" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="S34" s="5" t="str">
         <f>IF(A34="","",IF(H34="Fechado","Fechado",IF(H34="Perdido","Perdido",IF(K34="","Sem data",IF(K34&lt;TODAY(),"Atrasado",IF(K34=TODAY(),"Hoje","Agendado")))))))</f>
-        <v/>
-      </c>
-      <c r="AD34" s="5">
+        <v>Sem data</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U34" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="V34" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="W34" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="X34" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y34" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB34" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="AC34" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="AD34" s="5" t="str">
         <f>IF(A34="","",IF(OR(AK34&lt;&gt;"Qualificado",Y34&lt;&gt;"Verificado",U34="",Z34="",AA34=""),"Pendente",IF(AND(Z34&gt;=7,AA34&gt;=6),"Alta",IF(AND(Z34&gt;=5,AA34&gt;=4),"Média","Baixa"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="19:30">
+        <v>Pendente</v>
+      </c>
+      <c r="AE34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF34" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="AG34" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH34" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="AI34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK34" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL34" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38">
       <c r="S35" s="5">
         <f>IF(A35="","",IF(H35="Fechado","Fechado",IF(H35="Perdido","Perdido",IF(K35="","Sem data",IF(K35&lt;TODAY(),"Atrasado",IF(K35=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3236,7 +5296,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="19:30">
+    <row r="36" spans="1:38">
       <c r="S36" s="5">
         <f>IF(A36="","",IF(H36="Fechado","Fechado",IF(H36="Perdido","Perdido",IF(K36="","Sem data",IF(K36&lt;TODAY(),"Atrasado",IF(K36=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3246,7 +5306,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="19:30">
+    <row r="37" spans="1:38">
       <c r="S37" s="5">
         <f>IF(A37="","",IF(H37="Fechado","Fechado",IF(H37="Perdido","Perdido",IF(K37="","Sem data",IF(K37&lt;TODAY(),"Atrasado",IF(K37=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3256,7 +5316,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="19:30">
+    <row r="38" spans="1:38">
       <c r="S38" s="5">
         <f>IF(A38="","",IF(H38="Fechado","Fechado",IF(H38="Perdido","Perdido",IF(K38="","Sem data",IF(K38&lt;TODAY(),"Atrasado",IF(K38=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3266,7 +5326,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="19:30">
+    <row r="39" spans="1:38">
       <c r="S39" s="5">
         <f>IF(A39="","",IF(H39="Fechado","Fechado",IF(H39="Perdido","Perdido",IF(K39="","Sem data",IF(K39&lt;TODAY(),"Atrasado",IF(K39=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3276,7 +5336,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="19:30">
+    <row r="40" spans="1:38">
       <c r="S40" s="5">
         <f>IF(A40="","",IF(H40="Fechado","Fechado",IF(H40="Perdido","Perdido",IF(K40="","Sem data",IF(K40&lt;TODAY(),"Atrasado",IF(K40=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3286,7 +5346,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="19:30">
+    <row r="41" spans="1:38">
       <c r="S41" s="5">
         <f>IF(A41="","",IF(H41="Fechado","Fechado",IF(H41="Perdido","Perdido",IF(K41="","Sem data",IF(K41&lt;TODAY(),"Atrasado",IF(K41=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3296,7 +5356,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="19:30">
+    <row r="42" spans="1:38">
       <c r="S42" s="5">
         <f>IF(A42="","",IF(H42="Fechado","Fechado",IF(H42="Perdido","Perdido",IF(K42="","Sem data",IF(K42&lt;TODAY(),"Atrasado",IF(K42=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3306,7 +5366,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="19:30">
+    <row r="43" spans="1:38">
       <c r="S43" s="5">
         <f>IF(A43="","",IF(H43="Fechado","Fechado",IF(H43="Perdido","Perdido",IF(K43="","Sem data",IF(K43&lt;TODAY(),"Atrasado",IF(K43=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3316,7 +5376,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="19:30">
+    <row r="44" spans="1:38">
       <c r="S44" s="5">
         <f>IF(A44="","",IF(H44="Fechado","Fechado",IF(H44="Perdido","Perdido",IF(K44="","Sem data",IF(K44&lt;TODAY(),"Atrasado",IF(K44=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3326,7 +5386,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="19:30">
+    <row r="45" spans="1:38">
       <c r="S45" s="5">
         <f>IF(A45="","",IF(H45="Fechado","Fechado",IF(H45="Perdido","Perdido",IF(K45="","Sem data",IF(K45&lt;TODAY(),"Atrasado",IF(K45=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3336,7 +5396,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="19:30">
+    <row r="46" spans="1:38">
       <c r="S46" s="5">
         <f>IF(A46="","",IF(H46="Fechado","Fechado",IF(H46="Perdido","Perdido",IF(K46="","Sem data",IF(K46&lt;TODAY(),"Atrasado",IF(K46=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3346,7 +5406,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="19:30">
+    <row r="47" spans="1:38">
       <c r="S47" s="5">
         <f>IF(A47="","",IF(H47="Fechado","Fechado",IF(H47="Perdido","Perdido",IF(K47="","Sem data",IF(K47&lt;TODAY(),"Atrasado",IF(K47=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -3356,7 +5416,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="19:30">
+    <row r="48" spans="1:38">
       <c r="S48" s="5">
         <f>IF(A48="","",IF(H48="Fechado","Fechado",IF(H48="Perdido","Perdido",IF(K48="","Sem data",IF(K48&lt;TODAY(),"Atrasado",IF(K48=TODAY(),"Hoje","Agendado")))))))</f>
         <v/>
@@ -5002,6 +7062,65 @@
     <hyperlink ref="AH16" r:id="rId40"/>
     <hyperlink ref="F17" r:id="rId41"/>
     <hyperlink ref="AH17" r:id="rId42"/>
+    <hyperlink ref="F18" r:id="rId43"/>
+    <hyperlink ref="V18" r:id="rId44"/>
+    <hyperlink ref="W18" r:id="rId45"/>
+    <hyperlink ref="F19" r:id="rId46"/>
+    <hyperlink ref="V19" r:id="rId47"/>
+    <hyperlink ref="W19" r:id="rId48"/>
+    <hyperlink ref="F20" r:id="rId49"/>
+    <hyperlink ref="V20" r:id="rId50"/>
+    <hyperlink ref="W20" r:id="rId51"/>
+    <hyperlink ref="F21" r:id="rId52"/>
+    <hyperlink ref="V21" r:id="rId53"/>
+    <hyperlink ref="W21" r:id="rId54"/>
+    <hyperlink ref="F22" r:id="rId55"/>
+    <hyperlink ref="V22" r:id="rId56"/>
+    <hyperlink ref="W22" r:id="rId57"/>
+    <hyperlink ref="F23" r:id="rId58"/>
+    <hyperlink ref="V23" r:id="rId59"/>
+    <hyperlink ref="W23" r:id="rId60"/>
+    <hyperlink ref="AH23" r:id="rId61"/>
+    <hyperlink ref="F24" r:id="rId62"/>
+    <hyperlink ref="V24" r:id="rId63"/>
+    <hyperlink ref="W24" r:id="rId64"/>
+    <hyperlink ref="AH24" r:id="rId65"/>
+    <hyperlink ref="F25" r:id="rId66"/>
+    <hyperlink ref="V25" r:id="rId67"/>
+    <hyperlink ref="W25" r:id="rId68"/>
+    <hyperlink ref="AH25" r:id="rId69"/>
+    <hyperlink ref="F26" r:id="rId70"/>
+    <hyperlink ref="V26" r:id="rId71"/>
+    <hyperlink ref="W26" r:id="rId72"/>
+    <hyperlink ref="AH26" r:id="rId73"/>
+    <hyperlink ref="F27" r:id="rId74"/>
+    <hyperlink ref="V27" r:id="rId75"/>
+    <hyperlink ref="W27" r:id="rId76"/>
+    <hyperlink ref="AH27" r:id="rId77"/>
+    <hyperlink ref="F28" r:id="rId78"/>
+    <hyperlink ref="V28" r:id="rId79"/>
+    <hyperlink ref="W28" r:id="rId80"/>
+    <hyperlink ref="F29" r:id="rId81"/>
+    <hyperlink ref="V29" r:id="rId82"/>
+    <hyperlink ref="W29" r:id="rId83"/>
+    <hyperlink ref="AH29" r:id="rId84"/>
+    <hyperlink ref="F30" r:id="rId85"/>
+    <hyperlink ref="V30" r:id="rId86"/>
+    <hyperlink ref="W30" r:id="rId87"/>
+    <hyperlink ref="F31" r:id="rId88"/>
+    <hyperlink ref="V31" r:id="rId89"/>
+    <hyperlink ref="W31" r:id="rId90"/>
+    <hyperlink ref="AH31" r:id="rId91"/>
+    <hyperlink ref="F32" r:id="rId92"/>
+    <hyperlink ref="V32" r:id="rId93"/>
+    <hyperlink ref="W32" r:id="rId94"/>
+    <hyperlink ref="F33" r:id="rId95"/>
+    <hyperlink ref="V33" r:id="rId96"/>
+    <hyperlink ref="W33" r:id="rId97"/>
+    <hyperlink ref="F34" r:id="rId98"/>
+    <hyperlink ref="V34" r:id="rId99"/>
+    <hyperlink ref="W34" r:id="rId100"/>
+    <hyperlink ref="AH34" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -5036,7 +7155,7 @@
   <sheetData>
     <row r="1" spans="1:38" ht="32" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5461,7 +7580,7 @@
     <tabColor rgb="FF293E38"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL15"/>
+  <dimension ref="A1:AL32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.7109375" customWidth="1"/>
@@ -5483,7 +7602,7 @@
   <sheetData>
     <row r="1" spans="1:38" ht="32" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>196</v>
+        <v>319</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6773,8 +8892,1716 @@
         <v>194</v>
       </c>
     </row>
+    <row r="16" spans="1:38" ht="88" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="V16" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="X16" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC16" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="AD16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL16" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" ht="88" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="X17" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH17" s="3"/>
+      <c r="AI17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL17" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" ht="88" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="X18" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>2</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL18" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" ht="88" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="X19" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>4</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AC19" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL19" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" ht="88" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="X20" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL20" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" ht="88" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="W21" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="X21" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>6</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH21" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL21" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" ht="88" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="X22" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH22" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL22" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" ht="88" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="V23" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="W23" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="X23" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF23" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH23" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="AI23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL23" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" ht="88" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="X24" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="AD24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH24" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL24" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" ht="88" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="W25" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="X25" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB25" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="AC25" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="AD25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF25" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="AG25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH25" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="AI25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL25" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" ht="88" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="V26" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="W26" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="X26" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL26" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" ht="88" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="V27" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="W27" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="X27" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH27" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="AI27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ27" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL27" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" ht="88" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="V28" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="W28" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="X28" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>6</v>
+      </c>
+      <c r="AB28" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="AC28" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="AD28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL28" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" ht="88" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="W29" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="X29" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>6</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH29" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" ht="88" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="U30" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="V30" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="W30" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="X30" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="AC30" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="AD30" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE30" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG30" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ30" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK30" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL30" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" ht="88" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U31" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="V31" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="W31" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="X31" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>6</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>8</v>
+      </c>
+      <c r="AB31" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="AC31" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH31" s="3"/>
+      <c r="AI31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ31" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL31" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" ht="88" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="V32" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="W32" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="X32" s="1">
+        <v>46302</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>7</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH32" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK32" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL32" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:AL15"/>
+  <autoFilter ref="A4:AL32"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AL1"/>
     <mergeCell ref="A2:AL2"/>
@@ -6814,6 +10641,65 @@
     <hyperlink ref="AH14" r:id="rId32"/>
     <hyperlink ref="F15" r:id="rId33"/>
     <hyperlink ref="AH15" r:id="rId34"/>
+    <hyperlink ref="F16" r:id="rId35"/>
+    <hyperlink ref="V16" r:id="rId36"/>
+    <hyperlink ref="W16" r:id="rId37"/>
+    <hyperlink ref="F17" r:id="rId38"/>
+    <hyperlink ref="V17" r:id="rId39"/>
+    <hyperlink ref="W17" r:id="rId40"/>
+    <hyperlink ref="F18" r:id="rId41"/>
+    <hyperlink ref="V18" r:id="rId42"/>
+    <hyperlink ref="W18" r:id="rId43"/>
+    <hyperlink ref="F19" r:id="rId44"/>
+    <hyperlink ref="V19" r:id="rId45"/>
+    <hyperlink ref="W19" r:id="rId46"/>
+    <hyperlink ref="F20" r:id="rId47"/>
+    <hyperlink ref="V20" r:id="rId48"/>
+    <hyperlink ref="W20" r:id="rId49"/>
+    <hyperlink ref="F21" r:id="rId50"/>
+    <hyperlink ref="V21" r:id="rId51"/>
+    <hyperlink ref="W21" r:id="rId52"/>
+    <hyperlink ref="AH21" r:id="rId53"/>
+    <hyperlink ref="F22" r:id="rId54"/>
+    <hyperlink ref="V22" r:id="rId55"/>
+    <hyperlink ref="W22" r:id="rId56"/>
+    <hyperlink ref="AH22" r:id="rId57"/>
+    <hyperlink ref="F23" r:id="rId58"/>
+    <hyperlink ref="V23" r:id="rId59"/>
+    <hyperlink ref="W23" r:id="rId60"/>
+    <hyperlink ref="AH23" r:id="rId61"/>
+    <hyperlink ref="F24" r:id="rId62"/>
+    <hyperlink ref="V24" r:id="rId63"/>
+    <hyperlink ref="W24" r:id="rId64"/>
+    <hyperlink ref="AH24" r:id="rId65"/>
+    <hyperlink ref="F25" r:id="rId66"/>
+    <hyperlink ref="V25" r:id="rId67"/>
+    <hyperlink ref="W25" r:id="rId68"/>
+    <hyperlink ref="AH25" r:id="rId69"/>
+    <hyperlink ref="F26" r:id="rId70"/>
+    <hyperlink ref="V26" r:id="rId71"/>
+    <hyperlink ref="W26" r:id="rId72"/>
+    <hyperlink ref="F27" r:id="rId73"/>
+    <hyperlink ref="V27" r:id="rId74"/>
+    <hyperlink ref="W27" r:id="rId75"/>
+    <hyperlink ref="AH27" r:id="rId76"/>
+    <hyperlink ref="F28" r:id="rId77"/>
+    <hyperlink ref="V28" r:id="rId78"/>
+    <hyperlink ref="W28" r:id="rId79"/>
+    <hyperlink ref="F29" r:id="rId80"/>
+    <hyperlink ref="V29" r:id="rId81"/>
+    <hyperlink ref="W29" r:id="rId82"/>
+    <hyperlink ref="AH29" r:id="rId83"/>
+    <hyperlink ref="F30" r:id="rId84"/>
+    <hyperlink ref="V30" r:id="rId85"/>
+    <hyperlink ref="W30" r:id="rId86"/>
+    <hyperlink ref="F31" r:id="rId87"/>
+    <hyperlink ref="V31" r:id="rId88"/>
+    <hyperlink ref="W31" r:id="rId89"/>
+    <hyperlink ref="F32" r:id="rId90"/>
+    <hyperlink ref="V32" r:id="rId91"/>
+    <hyperlink ref="W32" r:id="rId92"/>
+    <hyperlink ref="AH32" r:id="rId93"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -6831,24 +10717,24 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>197</v>
+        <v>320</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>198</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>322</v>
       </c>
       <c r="B2" s="5">
         <f>COUNTA(CRM!A5:A204)</f>
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>200</v>
+        <v>323</v>
       </c>
       <c r="B3" s="5">
         <f>COUNTIF(CRM!AK5:AK204,"Qualificado")</f>
@@ -6857,16 +10743,16 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>201</v>
+        <v>324</v>
       </c>
       <c r="B4" s="5">
         <f>COUNTIF(CRM!AK5:AK204,"Pendente")</f>
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>325</v>
       </c>
       <c r="B5" s="5">
         <f>COUNTIF(CRM!AI5:AI204,"FORA DO BRASIL")</f>
@@ -6875,7 +10761,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>203</v>
+        <v>326</v>
       </c>
       <c r="B6" s="5">
         <f>COUNTIF(CRM!H5:H204,"Fechado")</f>
@@ -6884,7 +10770,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="B7" s="5">
         <f>COUNTIF(CRM!S5:S204,"Hoje")</f>
@@ -6893,7 +10779,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>205</v>
+        <v>328</v>
       </c>
       <c r="B8" s="5">
         <f>COUNTIF(CRM!S5:S204,"Atrasado")</f>
@@ -6902,7 +10788,7 @@
     </row>
     <row r="11" spans="1:2" ht="42" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>206</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -6921,90 +10807,90 @@
   <sheetData>
     <row r="1" spans="1:2" ht="35" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>207</v>
+        <v>330</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>208</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="100" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>332</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>210</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="100" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>211</v>
+        <v>334</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="100" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>336</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>214</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="100" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>215</v>
+        <v>338</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>216</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="100" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>218</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="100" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>342</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>220</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="100" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>221</v>
+        <v>344</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>222</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="100" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>223</v>
+        <v>346</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>224</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="100" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>225</v>
+        <v>348</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>226</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="100" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>228</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -7023,13 +10909,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>229</v>
+        <v>352</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>230</v>
+        <v>353</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>231</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="100" customHeight="1">
@@ -7037,10 +10923,10 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>232</v>
+        <v>355</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>233</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="100" customHeight="1">
@@ -7048,21 +10934,21 @@
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>234</v>
+        <v>357</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>235</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="100" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>236</v>
+        <v>359</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>237</v>
+        <v>360</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>238</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="100" customHeight="1">
@@ -7070,21 +10956,21 @@
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>239</v>
+        <v>362</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>240</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="100" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>241</v>
+        <v>364</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>242</v>
+        <v>365</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>243</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -7103,123 +10989,123 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>244</v>
+        <v>367</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>245</v>
+        <v>368</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>246</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="100" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>247</v>
+        <v>370</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>248</v>
+        <v>371</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>249</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="100" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>250</v>
+        <v>373</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>251</v>
+        <v>374</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>252</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="100" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>254</v>
+        <v>377</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="100" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>256</v>
+        <v>379</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>257</v>
+        <v>380</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>258</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="100" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>259</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>260</v>
+        <v>383</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>261</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="100" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>262</v>
+        <v>385</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>263</v>
+        <v>386</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>264</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="100" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>388</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>266</v>
+        <v>389</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>267</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="100" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>268</v>
+        <v>391</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>269</v>
+        <v>392</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>270</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="100" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>271</v>
+        <v>394</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>272</v>
+        <v>395</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>273</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="100" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>274</v>
+        <v>397</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>275</v>
+        <v>398</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>276</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -7229,7 +11115,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.7109375" customWidth="1"/>
@@ -7238,13 +11124,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>277</v>
+        <v>400</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>278</v>
+        <v>401</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>279</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="100" customHeight="1">
@@ -7252,10 +11138,10 @@
         <v>49</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>280</v>
+        <v>403</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>281</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="100" customHeight="1">
@@ -7263,10 +11149,10 @@
         <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>282</v>
+        <v>405</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>283</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="100" customHeight="1">
@@ -7274,10 +11160,10 @@
         <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>284</v>
+        <v>407</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>285</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="100" customHeight="1">
@@ -7285,10 +11171,10 @@
         <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>286</v>
+        <v>409</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>287</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="100" customHeight="1">
@@ -7296,10 +11182,10 @@
         <v>99</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>288</v>
+        <v>411</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>289</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="100" customHeight="1">
@@ -7307,10 +11193,10 @@
         <v>108</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>290</v>
+        <v>413</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>291</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="100" customHeight="1">
@@ -7318,10 +11204,10 @@
         <v>118</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>292</v>
+        <v>415</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>293</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="100" customHeight="1">
@@ -7329,10 +11215,10 @@
         <v>126</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>294</v>
+        <v>417</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>295</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="100" customHeight="1">
@@ -7340,10 +11226,10 @@
         <v>140</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>296</v>
+        <v>419</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>297</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="100" customHeight="1">
@@ -7351,10 +11237,10 @@
         <v>150</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>298</v>
+        <v>421</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>299</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="100" customHeight="1">
@@ -7362,10 +11248,10 @@
         <v>161</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>300</v>
+        <v>423</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>301</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="100" customHeight="1">
@@ -7373,10 +11259,10 @@
         <v>173</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>302</v>
+        <v>425</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>303</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="100" customHeight="1">
@@ -7384,32 +11270,219 @@
         <v>183</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>304</v>
+        <v>427</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>305</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="100" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>306</v>
+        <v>195</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>307</v>
+        <v>429</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>308</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="100" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>309</v>
+        <v>203</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="100" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="100" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="100" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="100" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="100" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="100" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="100" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="100" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="100" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="100" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="100" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="100" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="100" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="100" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="100" customHeight="1">
+      <c r="A31" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>311</v>
+      <c r="B31" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="100" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="100" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>
